--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2672DF06-2341-4B68-BE3A-E71576FA149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF3BFA7-CD69-47BB-B084-85D9BCDC8C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="480" windowWidth="24255" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3570" yWindow="1410" windowWidth="18810" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>SQL Saturday Richmond 2026 (#1135)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Joinville 2026 (#1139)</t>
+  </si>
+  <si>
+    <t>SeaQL 2026 - Brouwersdam, NL (#1140)</t>
   </si>
 </sst>
 </file>
@@ -155,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -190,6 +196,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -553,7 +565,7 @@
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>46081</v>
+        <v>46256</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>11</v>
@@ -594,8 +606,12 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="8">
@@ -604,8 +620,12 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="16">
+        <v>46130</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="8">
@@ -839,8 +859,10 @@
     <hyperlink ref="B3" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{3CC0F7AB-4490-4C03-A3EA-563AE4BBFA78}"/>
     <hyperlink ref="B4" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{26A80E05-1ED5-4017-BDE7-5BD71AB84731}"/>
     <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{5C0AE02A-E37D-4F8C-9894-10DBF52A6F4F}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{59FC6D52-C447-4042-A6E8-6B02210F740F}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF3BFA7-CD69-47BB-B084-85D9BCDC8C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E7A9D-CAED-47DD-8BD1-10260D1810F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="1410" windowWidth="18810" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20790" yWindow="555" windowWidth="19965" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>SeaQL 2026 - Brouwersdam, NL (#1140)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Sao Paulo 2026 (#1142)</t>
   </si>
 </sst>
 </file>
@@ -584,11 +587,15 @@
       <c r="B4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="C4" s="7">
+        <v>464</v>
+      </c>
+      <c r="D4" s="7">
+        <v>257</v>
+      </c>
       <c r="E4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.44612068965517243</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -634,13 +641,21 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="A8" s="5">
+        <v>46109</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="7">
+        <v>220</v>
+      </c>
+      <c r="D8" s="7">
+        <v>200</v>
+      </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -861,8 +876,9 @@
     <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{5C0AE02A-E37D-4F8C-9894-10DBF52A6F4F}"/>
     <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{59FC6D52-C447-4042-A6E8-6B02210F740F}"/>
     <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E7A9D-CAED-47DD-8BD1-10260D1810F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2F0475-BB90-4892-B421-1063614FBF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20790" yWindow="555" windowWidth="19965" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27210" yWindow="210" windowWidth="24465" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>SQL Saturday Sao Paulo 2026 (#1142)</t>
+  </si>
+  <si>
+    <t>Day of Data Richmond 2026 (#1135)</t>
   </si>
 </sst>
 </file>
@@ -659,16 +662,30 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="9">
+        <v>167</v>
+      </c>
+      <c r="D9" s="9">
+        <v>96</v>
+      </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42514970059880242</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="8">
@@ -877,8 +894,10 @@
     <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{59FC6D52-C447-4042-A6E8-6B02210F740F}"/>
     <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
     <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{6A71CCDA-7470-4C2B-A96E-07211211B3F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2F0475-BB90-4892-B421-1063614FBF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6254447E-05CB-4F42-9A59-2EF72F312BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27210" yWindow="210" windowWidth="24465" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -516,17 +516,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +555,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>46039</v>
       </c>
@@ -569,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>46256</v>
       </c>
@@ -583,7 +583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46102</v>
       </c>
@@ -601,35 +601,43 @@
         <v>0.44612068965517243</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>46123</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="7">
+        <v>167</v>
+      </c>
+      <c r="D5" s="7">
+        <v>96</v>
+      </c>
       <c r="E5" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.42514970059880242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>46123</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="C6" s="7">
+        <v>680</v>
+      </c>
+      <c r="D6" s="7">
+        <v>450</v>
+      </c>
       <c r="E6" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.33823529411764708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>46130</v>
       </c>
@@ -643,7 +651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>46109</v>
       </c>
@@ -661,7 +669,7 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>46123</v>
       </c>
@@ -679,7 +687,7 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>46123</v>
       </c>
@@ -693,7 +701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -703,7 +711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -713,7 +721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -723,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -733,7 +741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -743,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="E16" s="8">
@@ -751,7 +759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="E17" s="8">
@@ -759,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="E18" s="8">
@@ -770,7 +778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19" s="8">
@@ -778,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20" s="8">
@@ -786,7 +794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21" s="8">
@@ -794,7 +802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="13"/>
       <c r="E22" s="8">
@@ -802,7 +810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="E23" s="8">
@@ -810,7 +818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
       <c r="E24" s="8">
@@ -818,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
       <c r="E25" s="8">
@@ -826,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="13"/>
       <c r="E26" s="8">
@@ -834,7 +842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="13"/>
       <c r="E27" s="8">
@@ -842,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="13"/>
       <c r="E28" s="8">
@@ -850,37 +858,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="13"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="14"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="10"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="10"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="10"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="10"/>
       <c r="E35" s="8"/>

--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6254447E-05CB-4F42-9A59-2EF72F312BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861FC0BE-4D7D-4629-A85C-7EE4E4DECCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Date</t>
   </si>
@@ -562,11 +562,15 @@
       <c r="B2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="7">
+        <v>298</v>
+      </c>
+      <c r="D2" s="7">
+        <v>108</v>
+      </c>
       <c r="E2" s="8">
         <f t="shared" ref="E2:E28" si="0">IF(C2=0,0,+(C2-D2)/C2)</f>
-        <v>0</v>
+        <v>0.63758389261744963</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -691,9 +695,7 @@
       <c r="A10" s="5">
         <v>46123</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>14</v>
-      </c>
+      <c r="B10" s="13"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="8">
@@ -903,9 +905,8 @@
     <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
     <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
     <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
-    <hyperlink ref="B10" r:id="rId9" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{6A71CCDA-7470-4C2B-A96E-07211211B3F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861FC0BE-4D7D-4629-A85C-7EE4E4DECCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A48E6-B8B9-4BB3-817B-E1DB5CF6B3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="300" windowWidth="24465" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Date</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Day of Data Richmond 2026 (#1135)</t>
+  </si>
+  <si>
+    <t>Houston Ai-Lytics Day 2026 (#1137)</t>
   </si>
 </sst>
 </file>
@@ -516,17 +519,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,7 +558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46039</v>
       </c>
@@ -573,7 +576,7 @@
         <v>0.63758389261744963</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46256</v>
       </c>
@@ -587,7 +590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46102</v>
       </c>
@@ -605,7 +608,7 @@
         <v>0.44612068965517243</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46123</v>
       </c>
@@ -623,7 +626,7 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46123</v>
       </c>
@@ -641,7 +644,7 @@
         <v>0.33823529411764708</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>46130</v>
       </c>
@@ -655,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46109</v>
       </c>
@@ -673,7 +676,7 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46123</v>
       </c>
@@ -691,7 +694,7 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>46123</v>
       </c>
@@ -703,17 +706,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7">
+        <v>156</v>
+      </c>
+      <c r="D11" s="7">
+        <v>145</v>
+      </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7.0512820512820512E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
@@ -723,7 +734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="7"/>
@@ -733,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -743,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -753,7 +764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="E16" s="8">
@@ -761,7 +772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="E17" s="8">
@@ -769,7 +780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="E18" s="8">
@@ -780,7 +791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19" s="8">
@@ -788,7 +799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20" s="8">
@@ -796,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21" s="8">
@@ -804,7 +815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="13"/>
       <c r="E22" s="8">
@@ -812,7 +823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="E23" s="8">
@@ -820,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
       <c r="E24" s="8">
@@ -828,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
       <c r="E25" s="8">
@@ -836,7 +847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="13"/>
       <c r="E26" s="8">
@@ -844,7 +855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="13"/>
       <c r="E27" s="8">
@@ -852,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="13"/>
       <c r="E28" s="8">
@@ -860,37 +871,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="13"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="14"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="10"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="10"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="10"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="10"/>
       <c r="E35" s="8"/>
@@ -905,8 +916,9 @@
     <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
     <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
     <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
+    <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{CBF1FDBB-4936-434E-A18B-A7006D90C96F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A48E6-B8B9-4BB3-817B-E1DB5CF6B3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2CEFEF-6379-46B5-855A-14149B8CABF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="300" windowWidth="24465" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>Houston Ai-Lytics Day 2026 (#1137)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Arequipa 2026 (#1147)</t>
+  </si>
+  <si>
+    <t>Day of Data Jacksonville 2026 (#1128) </t>
+  </si>
+  <si>
+    <t>SQL Saturday Haiti 2026 (#1145) - Virtual -</t>
   </si>
 </sst>
 </file>
@@ -519,17 +528,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>46039</v>
       </c>
@@ -576,7 +585,7 @@
         <v>0.63758389261744963</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>46256</v>
       </c>
@@ -590,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46102</v>
       </c>
@@ -608,7 +617,7 @@
         <v>0.44612068965517243</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>46123</v>
       </c>
@@ -626,7 +635,7 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>46123</v>
       </c>
@@ -644,7 +653,7 @@
         <v>0.33823529411764708</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>46130</v>
       </c>
@@ -658,7 +667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>46109</v>
       </c>
@@ -676,7 +685,7 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>46123</v>
       </c>
@@ -694,19 +703,25 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+        <v>46137</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46</v>
+      </c>
+      <c r="D10" s="7">
+        <v>42</v>
+      </c>
       <c r="E10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>46137</v>
       </c>
@@ -724,9 +739,13 @@
         <v>7.0512820512820512E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="8">
@@ -734,9 +753,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="8">
@@ -744,7 +767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -754,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -764,7 +787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="E16" s="8">
@@ -772,7 +795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="E17" s="8">
@@ -780,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="E18" s="8">
@@ -791,7 +814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19" s="8">
@@ -799,7 +822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20" s="8">
@@ -807,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21" s="8">
@@ -815,7 +838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="13"/>
       <c r="E22" s="8">
@@ -823,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="E23" s="8">
@@ -831,7 +854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
       <c r="E24" s="8">
@@ -839,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
       <c r="E25" s="8">
@@ -847,7 +870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="13"/>
       <c r="E26" s="8">
@@ -855,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="13"/>
       <c r="E27" s="8">
@@ -863,7 +886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="13"/>
       <c r="E28" s="8">
@@ -871,37 +894,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="13"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="14"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="10"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="10"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="10"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="10"/>
       <c r="E35" s="8"/>
@@ -917,8 +940,11 @@
     <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
     <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
     <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{CBF1FDBB-4936-434E-A18B-A7006D90C96F}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{52A6CAD9-6FF4-4021-AF96-9A11F100CAB7}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{C267197A-EBDF-43AC-A57A-47836385B40A}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{7DE4CF3A-72E8-4101-9C80-B98C8F772699}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2CEFEF-6379-46B5-855A-14149B8CABF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FD44D8-8219-41AA-8473-DA96CFE00685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="1" r:id="rId1"/>
+    <sheet name="Jobs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -99,6 +100,24 @@
   </si>
   <si>
     <t>SQL Saturday Haiti 2026 (#1145) - Virtual -</t>
+  </si>
+  <si>
+    <t>App Developers</t>
+  </si>
+  <si>
+    <t>Architects</t>
+  </si>
+  <si>
+    <t>DBA</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -179,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -220,6 +239,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -746,11 +768,15 @@
       <c r="B12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="C12" s="7">
+        <v>534</v>
+      </c>
+      <c r="D12" s="7">
+        <v>371</v>
+      </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30524344569288392</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -947,4 +973,179 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808A6323-B2BF-43D1-9683-02EA2191A089}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
+        <v>46039</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
+        <v>46256</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>46102</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>46130</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>46109</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>24</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>106</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <f>26+25+27+35+36+53</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://sqlsaturday.com/2026-01-17-sqlsaturday1138/" xr:uid="{9BBFD336-5B49-4106-BC82-48F7FFABB181}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{14C4551B-AA3E-4854-A92B-107A1E3BF749}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{F69FEBB5-069E-4C66-B75B-65A012C62472}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{8B84D329-68E7-4FFB-8C69-5324DD0D507F}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{702A258F-A47A-449A-93A2-03B9D0A0FE5B}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{13A062FC-4BB7-410F-BC60-3CCF509AEAD9}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{DF840437-E1D6-4D9E-A7F8-BE10A89F7E2F}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{2CE9A7B7-C3DC-4953-915F-CBEE0F466C68}"/>
+    <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{0878FD0D-0661-4DB7-AF7D-D259D14FB142}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{2C514026-1108-4AEB-8461-B9A1F2D310C3}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{97D3C2E9-D00E-4F8C-BD01-85CF5D6C0A48}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{F6225BAC-FC20-4114-BB21-C62C7006DBDF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A48E6-B8B9-4BB3-817B-E1DB5CF6B3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FD44D8-8219-41AA-8473-DA96CFE00685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="300" windowWidth="24465" windowHeight="15315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="1" r:id="rId1"/>
+    <sheet name="Jobs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -90,6 +91,33 @@
   </si>
   <si>
     <t>Houston Ai-Lytics Day 2026 (#1137)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Arequipa 2026 (#1147)</t>
+  </si>
+  <si>
+    <t>Day of Data Jacksonville 2026 (#1128) </t>
+  </si>
+  <si>
+    <t>SQL Saturday Haiti 2026 (#1145) - Virtual -</t>
+  </si>
+  <si>
+    <t>App Developers</t>
+  </si>
+  <si>
+    <t>Architects</t>
+  </si>
+  <si>
+    <t>DBA</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -170,7 +198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -211,6 +239,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -519,17 +550,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>46039</v>
       </c>
@@ -576,7 +607,7 @@
         <v>0.63758389261744963</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>46256</v>
       </c>
@@ -590,7 +621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46102</v>
       </c>
@@ -608,7 +639,7 @@
         <v>0.44612068965517243</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>46123</v>
       </c>
@@ -626,7 +657,7 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>46123</v>
       </c>
@@ -644,7 +675,7 @@
         <v>0.33823529411764708</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16">
         <v>46130</v>
       </c>
@@ -658,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>46109</v>
       </c>
@@ -676,7 +707,7 @@
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>46123</v>
       </c>
@@ -694,19 +725,25 @@
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+        <v>46137</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46</v>
+      </c>
+      <c r="D10" s="7">
+        <v>42</v>
+      </c>
       <c r="E10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>46137</v>
       </c>
@@ -724,19 +761,31 @@
         <v>7.0512820512820512E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7">
+        <v>534</v>
+      </c>
+      <c r="D12" s="7">
+        <v>371</v>
+      </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
+        <v>0.30524344569288392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>21</v>
+      </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="8">
@@ -744,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7"/>
@@ -754,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7"/>
@@ -764,7 +813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="E16" s="8">
@@ -772,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="E17" s="8">
@@ -780,7 +829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="E18" s="8">
@@ -791,7 +840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19" s="8">
@@ -799,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20" s="8">
@@ -807,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21" s="8">
@@ -815,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="13"/>
       <c r="E22" s="8">
@@ -823,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="13"/>
       <c r="E23" s="8">
@@ -831,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="13"/>
       <c r="E24" s="8">
@@ -839,7 +888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="13"/>
       <c r="E25" s="8">
@@ -847,7 +896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="13"/>
       <c r="E26" s="8">
@@ -855,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="13"/>
       <c r="E27" s="8">
@@ -863,7 +912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="13"/>
       <c r="E28" s="8">
@@ -871,37 +920,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="13"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="14"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="10"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="10"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="10"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="10"/>
       <c r="E35" s="8"/>
@@ -917,8 +966,186 @@
     <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
     <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
     <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{CBF1FDBB-4936-434E-A18B-A7006D90C96F}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{52A6CAD9-6FF4-4021-AF96-9A11F100CAB7}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{C267197A-EBDF-43AC-A57A-47836385B40A}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{7DE4CF3A-72E8-4101-9C80-B98C8F772699}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId10"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808A6323-B2BF-43D1-9683-02EA2191A089}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
+        <v>46039</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
+        <v>46256</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>46102</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17">
+        <v>46130</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>46109</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>24</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>106</v>
+      </c>
+      <c r="G12">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <f>26+25+27+35+36+53</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://sqlsaturday.com/2026-01-17-sqlsaturday1138/" xr:uid="{9BBFD336-5B49-4106-BC82-48F7FFABB181}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{14C4551B-AA3E-4854-A92B-107A1E3BF749}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{F69FEBB5-069E-4C66-B75B-65A012C62472}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{8B84D329-68E7-4FFB-8C69-5324DD0D507F}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{702A258F-A47A-449A-93A2-03B9D0A0FE5B}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{13A062FC-4BB7-410F-BC60-3CCF509AEAD9}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{DF840437-E1D6-4D9E-A7F8-BE10A89F7E2F}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{2CE9A7B7-C3DC-4953-915F-CBEE0F466C68}"/>
+    <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{0878FD0D-0661-4DB7-AF7D-D259D14FB142}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{2C514026-1108-4AEB-8461-B9A1F2D310C3}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{97D3C2E9-D00E-4F8C-BD01-85CF5D6C0A48}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{F6225BAC-FC20-4114-BB21-C62C7006DBDF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve.jones\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FD44D8-8219-41AA-8473-DA96CFE00685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAD9E81-0EDB-42A6-BA34-AB1FF6BA8371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24150" yWindow="225" windowWidth="24180" windowHeight="14175" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -75,9 +75,6 @@
     <t>SQL Saturday Atlanta 2026 - AI &amp; BI (#1127)</t>
   </si>
   <si>
-    <t>SQL Saturday Richmond 2026 (#1135)</t>
-  </si>
-  <si>
     <t>SQL Saturday Joinville 2026 (#1139)</t>
   </si>
   <si>
@@ -96,35 +93,72 @@
     <t>SQL Saturday Arequipa 2026 (#1147)</t>
   </si>
   <si>
-    <t>Day of Data Jacksonville 2026 (#1128) </t>
-  </si>
-  <si>
-    <t>SQL Saturday Haiti 2026 (#1145) - Virtual -</t>
-  </si>
-  <si>
-    <t>App Developers</t>
+    <t>Day of Data Jacksonville 2026 (#1128)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Haiti 2026 (#1145) - Virtual</t>
   </si>
   <si>
     <t>Architects</t>
   </si>
   <si>
+    <t>App Dev</t>
+  </si>
+  <si>
     <t>DBA</t>
   </si>
   <si>
     <t>Data Engineer</t>
   </si>
   <si>
-    <t>Student</t>
-  </si>
-  <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Day of Data Raleigh 2026 (#1143)</t>
+  </si>
+  <si>
+    <t>Day of Data Wellington 2026 (#1146)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Croatia 2026 (#1134)</t>
+  </si>
+  <si>
+    <t>SQL Saturday CXS 2026 (#1151)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Austin 2026 (#1154)</t>
+  </si>
+  <si>
+    <t>Day of Data Baton Rouge 2026 (#1141)</t>
+  </si>
+  <si>
+    <t>Day of Data Albany 2026 (#1144)</t>
+  </si>
+  <si>
+    <t>Salt Lake City Day of Data 2026 (#1152)</t>
+  </si>
+  <si>
+    <t>Boston Data and AI Saturday 2026 (#1150)</t>
+  </si>
+  <si>
+    <t>Day of Data St Louis 2026 (#1148)</t>
+  </si>
+  <si>
+    <t>SQL Saturday Minnesota 2026 (#1153)</t>
+  </si>
+  <si>
+    <t>Day of Data PNW 2026 (#1149)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -149,13 +183,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -165,6 +192,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,11 +228,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -215,9 +250,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -225,26 +257,32 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -549,18 +587,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.54296875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,563 +627,1285 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46039</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>298</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>108</v>
       </c>
-      <c r="E2" s="8">
-        <f t="shared" ref="E2:E28" si="0">IF(C2=0,0,+(C2-D2)/C2)</f>
+      <c r="E2" s="7">
+        <f t="shared" ref="E2:E26" si="0">IF(C2=0,0,+(C2-D2)/C2)</f>
         <v>0.63758389261744963</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>46256</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46102</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6">
+        <v>464</v>
+      </c>
+      <c r="D3" s="6">
+        <v>257</v>
+      </c>
+      <c r="E3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.44612068965517243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>46102</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7">
-        <v>464</v>
-      </c>
-      <c r="D4" s="7">
-        <v>257</v>
-      </c>
-      <c r="E4" s="8">
-        <f t="shared" si="0"/>
-        <v>0.44612068965517243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46109</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="6">
+        <v>220</v>
+      </c>
+      <c r="D4" s="6">
+        <v>200</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46123</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
+        <v>680</v>
+      </c>
+      <c r="D5" s="6">
+        <v>450</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>0.33823529411764708</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>46123</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="17">
         <v>167</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D6" s="17">
         <v>96</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
         <v>0.42514970059880242</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B6" s="13" t="s">
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>46130</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7">
-        <v>680</v>
-      </c>
-      <c r="D6" s="7">
-        <v>450</v>
-      </c>
-      <c r="E6" s="8">
-        <f t="shared" si="0"/>
-        <v>0.33823529411764708</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16">
-        <v>46130</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="6">
+        <v>134</v>
+      </c>
+      <c r="D7" s="6">
+        <v>118</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>0.11940298507462686</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>46109</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="7">
-        <v>220</v>
-      </c>
-      <c r="D8" s="7">
-        <v>200</v>
-      </c>
-      <c r="E8" s="8">
-        <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46137</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="18">
+        <v>156</v>
+      </c>
+      <c r="D8" s="18">
+        <v>145</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="0"/>
+        <v>7.0512820512820512E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="9">
-        <v>167</v>
-      </c>
-      <c r="D9" s="9">
-        <v>96</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="0"/>
-        <v>0.42514970059880242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46137</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6">
+        <v>64</v>
+      </c>
+      <c r="D9" s="6">
+        <v>42</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="0"/>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>46137</v>
-      </c>
-      <c r="B10" s="13" t="s">
+        <v>46144</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="7">
-        <v>46</v>
-      </c>
-      <c r="D10" s="7">
-        <v>42</v>
-      </c>
-      <c r="E10" s="8">
-        <f t="shared" si="0"/>
-        <v>8.6956521739130432E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="6">
+        <v>534</v>
+      </c>
+      <c r="D10" s="6">
+        <v>371</v>
+      </c>
+      <c r="E10" s="7">
+        <f t="shared" si="0"/>
+        <v>0.30524344569288392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>46137</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7">
-        <v>156</v>
-      </c>
-      <c r="D11" s="7">
-        <v>145</v>
-      </c>
-      <c r="E11" s="8">
-        <f t="shared" si="0"/>
-        <v>7.0512820512820512E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46158</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6">
+        <v>70</v>
+      </c>
+      <c r="D11" s="6">
+        <v>107</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.52857142857142858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>46144</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7">
-        <v>534</v>
-      </c>
-      <c r="D12" s="7">
-        <v>371</v>
-      </c>
-      <c r="E12" s="8">
-        <f t="shared" si="0"/>
-        <v>0.30524344569288392</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>46256</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>46158</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="E17" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I18" t="s">
+        <v>46165</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>46172</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="6">
+        <v>36</v>
+      </c>
+      <c r="D14" s="6">
+        <v>25</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.30555555555555558</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>46186</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="6">
+        <v>153</v>
+      </c>
+      <c r="D15" s="6">
+        <v>146</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="0"/>
+        <v>4.5751633986928102E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>46200</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="6">
+        <v>196</v>
+      </c>
+      <c r="D16" s="6">
+        <v>128</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="0"/>
+        <v>0.34693877551020408</v>
+      </c>
+      <c r="I16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="13"/>
-      <c r="E22" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="13"/>
-      <c r="E23" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="13"/>
-      <c r="E24" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="13"/>
-      <c r="E25" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>46200</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="6">
+        <v>94</v>
+      </c>
+      <c r="D17" s="6">
+        <v>81</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.13829787234042554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>46221</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>46242</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>46256</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <f>IF(C20=0,0,+(C20-D20)/C20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <v>46284</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>46298</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>46319</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>46319</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>46333</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="13"/>
-      <c r="E26" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="12"/>
+      <c r="E26" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="13"/>
-      <c r="E27" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="12"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="13"/>
-      <c r="E28" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="13"/>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="9"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="14"/>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="9"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="10"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="9"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" s="10"/>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="9"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
-      <c r="B33" s="10"/>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="10"/>
-      <c r="E34" s="8"/>
-    </row>
-    <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="10"/>
-      <c r="E35" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="E33" s="7"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
+    <sortCondition ref="A2:A34"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://sqlsaturday.com/2026-01-17-sqlsaturday1138/" xr:uid="{82BDF17B-780C-46C4-BDF3-6B50D2949365}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{3CC0F7AB-4490-4C03-A3EA-563AE4BBFA78}"/>
-    <hyperlink ref="B4" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{26A80E05-1ED5-4017-BDE7-5BD71AB84731}"/>
-    <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{5C0AE02A-E37D-4F8C-9894-10DBF52A6F4F}"/>
-    <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{59FC6D52-C447-4042-A6E8-6B02210F740F}"/>
-    <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
-    <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
-    <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
-    <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{CBF1FDBB-4936-434E-A18B-A7006D90C96F}"/>
-    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{52A6CAD9-6FF4-4021-AF96-9A11F100CAB7}"/>
-    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{C267197A-EBDF-43AC-A57A-47836385B40A}"/>
-    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{7DE4CF3A-72E8-4101-9C80-B98C8F772699}"/>
+    <hyperlink ref="B12" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{3CC0F7AB-4490-4C03-A3EA-563AE4BBFA78}"/>
+    <hyperlink ref="B3" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{26A80E05-1ED5-4017-BDE7-5BD71AB84731}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{59FC6D52-C447-4042-A6E8-6B02210F740F}"/>
+    <hyperlink ref="B7" r:id="rId5" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{58E6D6B4-5ED4-4714-8FDB-E08CF0662BC3}"/>
+    <hyperlink ref="B4" r:id="rId6" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{437241E0-0AAF-4D4E-8A16-325412A2DA23}"/>
+    <hyperlink ref="B6" r:id="rId7" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{0D895616-7215-4314-966E-B2E806332540}"/>
+    <hyperlink ref="B8" r:id="rId8" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{CBF1FDBB-4936-434E-A18B-A7006D90C96F}"/>
+    <hyperlink ref="B9" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{4F37EDCA-58B8-44A9-B0D6-6EDA7AF3E42B}"/>
+    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{6FA71D67-7C14-4F2A-9D00-36D7917E1905}"/>
+    <hyperlink ref="B11" r:id="rId11" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{621DEBD7-D2F3-4796-9A5B-835C7AC84D89}"/>
+    <hyperlink ref="B20" r:id="rId12" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{D5D65017-5D91-4956-91B6-8FD0826424E6}"/>
+    <hyperlink ref="B13" r:id="rId13" display="https://sqlsaturday.com/2026-05-23-sqlsaturday1143/" xr:uid="{08240465-5826-4B6D-BF89-D440EAEC6B19}"/>
+    <hyperlink ref="B14" r:id="rId14" display="https://sqlsaturday.com/2026-05-30-sqlsaturday1146/" xr:uid="{07BCAB4D-DB0C-47E4-80D6-972EFD2D8F00}"/>
+    <hyperlink ref="B15" r:id="rId15" display="https://sqlsaturday.com/2026-06-13-sqlsaturday1134/" xr:uid="{71407BD4-076C-49A9-9D7A-02703DA14C90}"/>
+    <hyperlink ref="B16" r:id="rId16" display="https://sqlsaturday.com/2026-06-27-sqlsaturday1151/" xr:uid="{D2572D5E-CAA7-4C8A-BC10-9BDD5367C374}"/>
+    <hyperlink ref="B17" r:id="rId17" display="https://sqlsaturday.com/2026-06-27-sqlsaturday1154/" xr:uid="{4E193433-7FEF-42F0-9BE1-2E1B4F56DC45}"/>
+    <hyperlink ref="B18" r:id="rId18" display="https://sqlsaturday.com/2026-07-18-sqlsaturday1141/" xr:uid="{B4310BB2-BE85-4D94-9531-7F04382A3C59}"/>
+    <hyperlink ref="B19" r:id="rId19" display="https://sqlsaturday.com/2026-08-08-sqlsaturday1144/" xr:uid="{49013F68-7251-4303-A8A8-19F4C344B133}"/>
+    <hyperlink ref="B21" r:id="rId20" display="https://sqlsaturday.com/2026-09-19-sqlsaturday1152/" xr:uid="{1C24212F-ACFE-4FD3-A6CF-8E691EEA9C75}"/>
+    <hyperlink ref="B22" r:id="rId21" display="https://sqlsaturday.com/2026-10-03-sqlsaturday1150/" xr:uid="{80072270-983F-4E6A-AFAE-3FC24DE448B3}"/>
+    <hyperlink ref="B23" r:id="rId22" display="https://sqlsaturday.com/2026-10-24-sqlsaturday1148/" xr:uid="{111A5B01-58C6-46AB-81AC-567A7B3C8861}"/>
+    <hyperlink ref="B24" r:id="rId23" display="https://sqlsaturday.com/2026-10-24-sqlsaturday1153/" xr:uid="{29A122E2-6150-4028-BEF4-E884CED9AA91}"/>
+    <hyperlink ref="B25" r:id="rId24" display="https://sqlsaturday.com/2026-11-07-sqlsaturday1149/" xr:uid="{1C87B471-8BB8-47E8-8A2F-FEB250EAF056}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808A6323-B2BF-43D1-9683-02EA2191A089}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9FAEBE-70DD-4114-ACD9-DE4988A37B44}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.453125" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" customWidth="1"/>
-    <col min="6" max="6" width="15.7265625" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="42.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" t="s">
         <v>22</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <f>+Attendance!A2</f>
         <v>46039</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="str">
+        <f>+Attendance!B2</f>
+        <v>SQL Saturday Lima 2026 (#1138)</v>
+      </c>
+      <c r="C2" s="19">
+        <v>42</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19">
+        <v>68</v>
+      </c>
+      <c r="F2" s="19">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8">
+        <f t="shared" ref="G2:G6" si="0">+H2-SUM(C2:F2)</f>
+        <v>188</v>
+      </c>
+      <c r="H2" s="8">
+        <f>+Attendance!C2</f>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <f>+Attendance!A3</f>
+        <v>46102</v>
+      </c>
+      <c r="B3" s="10" t="str">
+        <f>+Attendance!B3</f>
+        <v>SQL Saturday Atlanta 2026 - AI &amp; BI (#1127)</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19">
+        <v>0</v>
+      </c>
+      <c r="F3" s="19">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <f t="shared" si="0"/>
+        <v>464</v>
+      </c>
+      <c r="H3" s="8">
+        <f>+Attendance!C3</f>
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <f>+Attendance!A4</f>
+        <v>46109</v>
+      </c>
+      <c r="B4" s="10" t="str">
+        <f>+Attendance!B4</f>
+        <v>SQL Saturday Sao Paulo 2026 (#1142)</v>
+      </c>
+      <c r="C4" s="19">
+        <v>28</v>
+      </c>
+      <c r="D4" s="19">
+        <v>5</v>
+      </c>
+      <c r="E4" s="19">
+        <v>46</v>
+      </c>
+      <c r="F4" s="19">
+        <v>8</v>
+      </c>
+      <c r="G4" s="8">
+        <f t="shared" si="0"/>
+        <v>133</v>
+      </c>
+      <c r="H4" s="8">
+        <f>+Attendance!C4</f>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <f>+Attendance!A5</f>
+        <v>46123</v>
+      </c>
+      <c r="B5" s="10" t="str">
+        <f>+Attendance!B5</f>
+        <v>SQL Saturday Joinville 2026 (#1139)</v>
+      </c>
+      <c r="C5" s="19">
+        <v>29</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19">
+        <v>16</v>
+      </c>
+      <c r="F5" s="19">
+        <v>19</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="0"/>
+        <v>616</v>
+      </c>
+      <c r="H5" s="8">
+        <f>+Attendance!C5</f>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <f>+Attendance!A6</f>
+        <v>46123</v>
+      </c>
+      <c r="B6" s="10" t="str">
+        <f>+Attendance!B6</f>
+        <v>Day of Data Richmond 2026 (#1135)</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>31</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <f t="shared" si="0"/>
+        <v>123</v>
+      </c>
+      <c r="H6" s="8">
+        <f>+Attendance!C6</f>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <f>+Attendance!A7</f>
+        <v>46130</v>
+      </c>
+      <c r="B7" s="10" t="str">
+        <f>+Attendance!B7</f>
+        <v>SeaQL 2026 - Brouwersdam, NL (#1140)</v>
+      </c>
+      <c r="C7">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <f>4+3+1+2+1</f>
+        <v>11</v>
+      </c>
+      <c r="G7" s="8">
+        <f>+H7-SUM(C7:F7)</f>
+        <v>98</v>
+      </c>
+      <c r="H7" s="8">
+        <f>+Attendance!C7</f>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <f>+Attendance!A8</f>
+        <v>46137</v>
+      </c>
+      <c r="B8" s="10" t="str">
+        <f>+Attendance!B8</f>
+        <v>Houston Ai-Lytics Day 2026 (#1137)</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8">
+        <f t="shared" ref="G8:G9" si="1">+H8-SUM(C8:F8)</f>
+        <v>93</v>
+      </c>
+      <c r="H8" s="8">
+        <f>+Attendance!C8</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <f>+Attendance!A9</f>
+        <v>46137</v>
+      </c>
+      <c r="B9" s="10" t="str">
+        <f>+Attendance!B9</f>
+        <v>SQL Saturday Arequipa 2026 (#1147)</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="H9" s="8">
+        <f>+Attendance!C9</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <f>+Attendance!A10</f>
+        <v>46144</v>
+      </c>
+      <c r="B10" s="10" t="str">
+        <f>+Attendance!B10</f>
+        <v>Day of Data Jacksonville 2026 (#1128)</v>
+      </c>
+      <c r="C10">
+        <v>53</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>106</v>
+      </c>
+      <c r="G10" s="8">
+        <f>+H10-SUM(C10:F10)</f>
+        <v>290</v>
+      </c>
+      <c r="H10" s="8">
+        <f>+Attendance!C10</f>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <f>+Attendance!A11</f>
+        <v>46158</v>
+      </c>
+      <c r="B11" s="10" t="str">
+        <f>+Attendance!B11</f>
+        <v>SQL Saturday Haiti 2026 (#1145) - Virtual</v>
+      </c>
+      <c r="C11">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" ref="G11:G12" si="2">+H11-SUM(C11:F11)</f>
+        <v>48</v>
+      </c>
+      <c r="H11" s="8">
+        <f>+Attendance!C11</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <f>+Attendance!A12</f>
         <v>46256</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>46102</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17">
-        <v>46130</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>46109</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="B12" s="10" t="str">
+        <f>+Attendance!B12</f>
+        <v>SQL Saturday Belo Horizonte 2026 (#1132)</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <f>+Attendance!C12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <f>+Attendance!A13</f>
+        <v>46165</v>
+      </c>
+      <c r="B13" s="10" t="str">
+        <f>+Attendance!B13</f>
+        <v>Day of Data Raleigh 2026 (#1143)</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <f t="shared" ref="G13:G24" si="3">+H13-SUM(C13:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <f>+Attendance!C13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <f>+Attendance!A14</f>
+        <v>46172</v>
+      </c>
+      <c r="B14" s="10" t="str">
+        <f>+Attendance!B14</f>
+        <v>Day of Data Wellington 2026 (#1146)</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4</v>
+      </c>
+      <c r="H14" s="8">
+        <f>+Attendance!C14</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <f>+Attendance!A15</f>
+        <v>46186</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <f>+Attendance!B15</f>
+        <v>SQL Saturday Croatia 2026 (#1134)</v>
+      </c>
+      <c r="C15">
+        <v>22</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>19</v>
+      </c>
+      <c r="G15" s="8">
+        <v>72</v>
+      </c>
+      <c r="H15" s="8">
+        <f>+Attendance!C15</f>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <f>+Attendance!A16</f>
+        <v>46200</v>
+      </c>
+      <c r="B16" s="10" t="str">
+        <f>+Attendance!B16</f>
+        <v>SQL Saturday CXS 2026 (#1151)</v>
+      </c>
+      <c r="C16">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>46123</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>46137</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
-      <c r="F10">
-        <v>24</v>
-      </c>
-      <c r="G10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>46137</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="D16">
+        <v>42</v>
+      </c>
+      <c r="E16">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
-        <v>46144</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>53</v>
-      </c>
-      <c r="D12">
-        <v>40</v>
-      </c>
-      <c r="E12">
-        <v>45</v>
-      </c>
-      <c r="F12">
-        <v>106</v>
-      </c>
-      <c r="G12">
-        <v>25</v>
-      </c>
-      <c r="H12">
-        <f>26+25+27+35+36+53</f>
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>46158</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>21</v>
+      <c r="F16">
+        <v>31</v>
+      </c>
+      <c r="G16" s="8">
+        <v>23</v>
+      </c>
+      <c r="H16" s="8">
+        <f>+Attendance!C16</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <f>+Attendance!A17</f>
+        <v>46200</v>
+      </c>
+      <c r="B17" s="10" t="str">
+        <f>+Attendance!B17</f>
+        <v>SQL Saturday Austin 2026 (#1154)</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <f t="shared" si="3"/>
+        <v>94</v>
+      </c>
+      <c r="H17" s="8">
+        <f>+Attendance!C17</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <f>+Attendance!A18</f>
+        <v>46221</v>
+      </c>
+      <c r="B18" s="10" t="str">
+        <f>+Attendance!B18</f>
+        <v>Day of Data Baton Rouge 2026 (#1141)</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <f>+Attendance!C18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <f>+Attendance!A19</f>
+        <v>46242</v>
+      </c>
+      <c r="B19" s="10" t="str">
+        <f>+Attendance!B19</f>
+        <v>Day of Data Albany 2026 (#1144)</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <f>+Attendance!C19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <f>+Attendance!A20</f>
+        <v>46256</v>
+      </c>
+      <c r="B20" s="10" t="str">
+        <f>+Attendance!B20</f>
+        <v>SQL Saturday Belo Horizonte 2026 (#1132)</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <f>+Attendance!C20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
+        <f>+Attendance!A21</f>
+        <v>46284</v>
+      </c>
+      <c r="B21" s="10" t="str">
+        <f>+Attendance!B21</f>
+        <v>Salt Lake City Day of Data 2026 (#1152)</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <f>+Attendance!C21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <f>+Attendance!A22</f>
+        <v>46298</v>
+      </c>
+      <c r="B22" s="10" t="str">
+        <f>+Attendance!B22</f>
+        <v>Boston Data and AI Saturday 2026 (#1150)</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <f>+Attendance!C22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <f>+Attendance!A23</f>
+        <v>46319</v>
+      </c>
+      <c r="B23" s="10" t="str">
+        <f>+Attendance!B23</f>
+        <v>Day of Data St Louis 2026 (#1148)</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <f>+Attendance!C23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <f>+Attendance!A24</f>
+        <v>46319</v>
+      </c>
+      <c r="B24" s="10" t="str">
+        <f>+Attendance!B24</f>
+        <v>SQL Saturday Minnesota 2026 (#1153)</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="8">
+        <f>+Attendance!C24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
+        <f>+Attendance!A25</f>
+        <v>46333</v>
+      </c>
+      <c r="B25" s="10" t="str">
+        <f>+Attendance!B25</f>
+        <v>Day of Data PNW 2026 (#1149)</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" ref="G25" si="4">+H25-SUM(C25:F25)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <f>+Attendance!C25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
+        <f>+Attendance!A26</f>
+        <v>0</v>
+      </c>
+      <c r="B26" s="10">
+        <f>+Attendance!B26</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://sqlsaturday.com/2026-01-17-sqlsaturday1138/" xr:uid="{9BBFD336-5B49-4106-BC82-48F7FFABB181}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://sqlsaturday.com/2026-02-28-sqlsaturday1132/" xr:uid="{14C4551B-AA3E-4854-A92B-107A1E3BF749}"/>
-    <hyperlink ref="B4" r:id="rId3" display="https://sqlsaturday.com/2026-03-21-sqlsaturday1127/" xr:uid="{F69FEBB5-069E-4C66-B75B-65A012C62472}"/>
-    <hyperlink ref="B5" r:id="rId4" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{8B84D329-68E7-4FFB-8C69-5324DD0D507F}"/>
-    <hyperlink ref="B6" r:id="rId5" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1139/" xr:uid="{702A258F-A47A-449A-93A2-03B9D0A0FE5B}"/>
-    <hyperlink ref="B7" r:id="rId6" display="https://sqlsaturday.com/2026-04-18-sqlsaturday1140/" xr:uid="{13A062FC-4BB7-410F-BC60-3CCF509AEAD9}"/>
-    <hyperlink ref="B8" r:id="rId7" display="https://sqlsaturday.com/2026-03-28-sqlsaturday1142/" xr:uid="{DF840437-E1D6-4D9E-A7F8-BE10A89F7E2F}"/>
-    <hyperlink ref="B9" r:id="rId8" display="https://sqlsaturday.com/2026-04-11-sqlsaturday1135/" xr:uid="{2CE9A7B7-C3DC-4953-915F-CBEE0F466C68}"/>
-    <hyperlink ref="B11" r:id="rId9" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1137/" xr:uid="{0878FD0D-0661-4DB7-AF7D-D259D14FB142}"/>
-    <hyperlink ref="B10" r:id="rId10" display="https://sqlsaturday.com/2026-04-25-sqlsaturday1147/" xr:uid="{2C514026-1108-4AEB-8461-B9A1F2D310C3}"/>
-    <hyperlink ref="B12" r:id="rId11" display="https://sqlsaturday.com/2026-05-02-sqlsaturday1128/" xr:uid="{97D3C2E9-D00E-4F8C-BD01-85CF5D6C0A48}"/>
-    <hyperlink ref="B13" r:id="rId12" display="https://sqlsaturday.com/2026-05-16-sqlsaturday1145/" xr:uid="{F6225BAC-FC20-4114-BB21-C62C7006DBDF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CAD9E81-0EDB-42A6-BA34-AB1FF6BA8371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFBF676-1384-4E42-9A5C-A73B70B8A893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24150" yWindow="225" windowWidth="24180" windowHeight="14175" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25845" yWindow="630" windowWidth="22860" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -833,14 +833,14 @@
         <v>27</v>
       </c>
       <c r="C13" s="6">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="D13" s="6">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.5393258426966292</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1530,11 +1530,11 @@
       </c>
       <c r="G13" s="8">
         <f t="shared" ref="G13:G24" si="3">+H13-SUM(C13:F13)</f>
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H13" s="8">
         <f>+Attendance!C13</f>
-        <v>0</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">

--- a/assets/misc/2026/2026_Attendance.xlsx
+++ b/assets/misc/2026/2026_Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\git\sqlsatwebsite\assets\misc\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFBF676-1384-4E42-9A5C-A73B70B8A893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EAE2CA-1540-470A-AC36-A41872D3AC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25845" yWindow="630" windowWidth="22860" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +203,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -233,7 +239,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -280,6 +286,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -926,14 +944,14 @@
         <v>32</v>
       </c>
       <c r="C18" s="6">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="D18" s="6">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="E18" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42880523731587561</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1142,15 +1160,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9FAEBE-70DD-4114-ACD9-DE4988A37B44}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="42.85546875" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1195,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f>+Attendance!A2</f>
         <v>46039</v>
@@ -1206,7 +1225,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>+Attendance!A3</f>
         <v>46102</v>
@@ -1236,7 +1255,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f>+Attendance!A4</f>
         <v>46109</v>
@@ -1266,7 +1285,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>+Attendance!A5</f>
         <v>46123</v>
@@ -1296,7 +1315,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f>+Attendance!A6</f>
         <v>46123</v>
@@ -1325,8 +1344,10 @@
         <f>+Attendance!C6</f>
         <v>167</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O6" s="20"/>
+      <c r="P6" s="23"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f>+Attendance!A7</f>
         <v>46130</v>
@@ -1356,8 +1377,10 @@
         <f>+Attendance!C7</f>
         <v>134</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O7" s="21"/>
+      <c r="P7" s="23"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f>+Attendance!A8</f>
         <v>46137</v>
@@ -1386,8 +1409,10 @@
         <f>+Attendance!C8</f>
         <v>156</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O8" s="21"/>
+      <c r="P8" s="22"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <f>+Attendance!A9</f>
         <v>46137</v>
@@ -1416,8 +1441,10 @@
         <f>+Attendance!C9</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O9" s="21"/>
+      <c r="P9" s="22"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f>+Attendance!A10</f>
         <v>46144</v>
@@ -1446,8 +1473,10 @@
         <f>+Attendance!C10</f>
         <v>534</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O10" s="21"/>
+      <c r="P10" s="22"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <f>+Attendance!A11</f>
         <v>46158</v>
@@ -1476,8 +1505,10 @@
         <f>+Attendance!C11</f>
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O11" s="21"/>
+      <c r="P11" s="22"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <f>+Attendance!A12</f>
         <v>46256</v>
@@ -1506,8 +1537,10 @@
         <f>+Attendance!C12</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O12" s="21"/>
+      <c r="P12" s="22"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <f>+Attendance!A13</f>
         <v>46165</v>
@@ -1536,8 +1569,10 @@
         <f>+Attendance!C13</f>
         <v>178</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O13" s="21"/>
+      <c r="P13" s="22"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f>+Attendance!A14</f>
         <v>46172</v>
@@ -1565,8 +1600,10 @@
         <f>+Attendance!C14</f>
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O14" s="21"/>
+      <c r="P14" s="22"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <f>+Attendance!A15</f>
         <v>46186</v>
@@ -1594,8 +1631,10 @@
         <f>+Attendance!C15</f>
         <v>153</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O15" s="21"/>
+      <c r="P15" s="22"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <f>+Attendance!A16</f>
         <v>46200</v>
@@ -1623,8 +1662,10 @@
         <f>+Attendance!C16</f>
         <v>196</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O16" s="21"/>
+      <c r="P16" s="22"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <f>+Attendance!A17</f>
         <v>46200</v>
@@ -1653,8 +1694,10 @@
         <f>+Attendance!C17</f>
         <v>94</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O17" s="21"/>
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <f>+Attendance!A18</f>
         <v>46221</v>
@@ -1664,27 +1707,29 @@
         <v>Day of Data Baton Rouge 2026 (#1141)</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G18" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>461</v>
       </c>
       <c r="H18" s="8">
         <f>+Attendance!C18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+      <c r="O18" s="21"/>
+      <c r="P18" s="22"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <f>+Attendance!A19</f>
         <v>46242</v>
@@ -1713,8 +1758,10 @@
         <f>+Attendance!C19</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O19" s="21"/>
+      <c r="P19" s="22"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <f>+Attendance!A20</f>
         <v>46256</v>
@@ -1743,8 +1790,10 @@
         <f>+Attendance!C20</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O20" s="21"/>
+      <c r="P20" s="22"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <f>+Attendance!A21</f>
         <v>46284</v>
@@ -1773,8 +1822,10 @@
         <f>+Attendance!C21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O21" s="21"/>
+      <c r="P21" s="22"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <f>+Attendance!A22</f>
         <v>46298</v>
@@ -1803,8 +1854,10 @@
         <f>+Attendance!C22</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O22" s="21"/>
+      <c r="P22" s="22"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <f>+Attendance!A23</f>
         <v>46319</v>
@@ -1833,8 +1886,10 @@
         <f>+Attendance!C23</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O23" s="21"/>
+      <c r="P23" s="22"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <f>+Attendance!A24</f>
         <v>46319</v>
@@ -1863,8 +1918,10 @@
         <f>+Attendance!C24</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O24" s="21"/>
+      <c r="P24" s="22"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <f>+Attendance!A25</f>
         <v>46333</v>
@@ -1893,8 +1950,10 @@
         <f>+Attendance!C25</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="O25" s="21"/>
+      <c r="P25" s="22"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <f>+Attendance!A26</f>
         <v>0</v>
@@ -1903,8 +1962,25 @@
         <f>+Attendance!B26</f>
         <v>0</v>
       </c>
+      <c r="O26" s="21"/>
+      <c r="P26" s="22"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O27" s="21"/>
+      <c r="P27" s="22"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O28" s="21"/>
+      <c r="P28" s="22"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O29" s="21"/>
+      <c r="P29" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P6:P7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
